--- a/outputs/q4/结果提交_Q4.xlsx
+++ b/outputs/q4/结果提交_Q4.xlsx
@@ -4076,32 +4076,32 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
@@ -4120,32 +4120,32 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>6</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2</v>
